--- a/result/突破幅度分析.xlsx
+++ b/result/突破幅度分析.xlsx
@@ -513,7 +513,7 @@
         <v>39</v>
       </c>
       <c r="C4" t="n">
-        <v>3.836666666666666</v>
+        <v>3.875641025641026</v>
       </c>
       <c r="D4" t="n">
         <v>6.69</v>
@@ -522,7 +522,7 @@
         <v>24.07</v>
       </c>
       <c r="F4" t="n">
-        <v>-49.83</v>
+        <v>-47.04</v>
       </c>
     </row>
     <row r="5">
@@ -535,7 +535,7 @@
         <v>50</v>
       </c>
       <c r="C5" t="n">
-        <v>5.1814</v>
+        <v>5.187799999999999</v>
       </c>
       <c r="D5" t="n">
         <v>7.175</v>
@@ -557,7 +557,7 @@
         <v>151</v>
       </c>
       <c r="C6" t="n">
-        <v>4.892715231788079</v>
+        <v>4.748145695364238</v>
       </c>
       <c r="D6" t="n">
         <v>6.7</v>
@@ -566,7 +566,7 @@
         <v>16.88</v>
       </c>
       <c r="F6" t="n">
-        <v>-59.35</v>
+        <v>-59.08</v>
       </c>
     </row>
     <row r="7">
@@ -579,7 +579,7 @@
         <v>266</v>
       </c>
       <c r="C7" t="n">
-        <v>3.499210526315789</v>
+        <v>3.472142857142857</v>
       </c>
       <c r="D7" t="n">
         <v>6.029999999999999</v>
@@ -588,7 +588,7 @@
         <v>196.3</v>
       </c>
       <c r="F7" t="n">
-        <v>-51.29</v>
+        <v>-51.88</v>
       </c>
     </row>
     <row r="8">

--- a/result/突破幅度分析.xlsx
+++ b/result/突破幅度分析.xlsx
@@ -579,10 +579,10 @@
         <v>266</v>
       </c>
       <c r="C7" t="n">
-        <v>3.472142857142857</v>
+        <v>5.149398496240601</v>
       </c>
       <c r="D7" t="n">
-        <v>6.029999999999999</v>
+        <v>6.065</v>
       </c>
       <c r="E7" t="n">
         <v>196.3</v>
@@ -601,13 +601,13 @@
         <v>66</v>
       </c>
       <c r="C8" t="n">
-        <v>2.779848484848485</v>
+        <v>3.589393939393939</v>
       </c>
       <c r="D8" t="n">
-        <v>-4.455</v>
+        <v>-6.75</v>
       </c>
       <c r="E8" t="n">
-        <v>62.67</v>
+        <v>65.02</v>
       </c>
       <c r="F8" t="n">
         <v>-19.77</v>

--- a/result/突破幅度分析.xlsx
+++ b/result/突破幅度分析.xlsx
@@ -513,7 +513,7 @@
         <v>39</v>
       </c>
       <c r="C4" t="n">
-        <v>3.875641025641026</v>
+        <v>3.802307692307692</v>
       </c>
       <c r="D4" t="n">
         <v>6.69</v>
@@ -522,7 +522,7 @@
         <v>24.07</v>
       </c>
       <c r="F4" t="n">
-        <v>-47.04</v>
+        <v>-48.03</v>
       </c>
     </row>
     <row r="5">
@@ -535,7 +535,7 @@
         <v>50</v>
       </c>
       <c r="C5" t="n">
-        <v>5.187799999999999</v>
+        <v>5.055</v>
       </c>
       <c r="D5" t="n">
         <v>7.175</v>
@@ -544,7 +544,7 @@
         <v>17.65</v>
       </c>
       <c r="F5" t="n">
-        <v>-37.5</v>
+        <v>-39.41</v>
       </c>
     </row>
     <row r="6">
@@ -557,7 +557,7 @@
         <v>151</v>
       </c>
       <c r="C6" t="n">
-        <v>4.748145695364238</v>
+        <v>4.703245033112583</v>
       </c>
       <c r="D6" t="n">
         <v>6.7</v>
@@ -566,7 +566,7 @@
         <v>16.88</v>
       </c>
       <c r="F6" t="n">
-        <v>-59.08</v>
+        <v>-61.2</v>
       </c>
     </row>
     <row r="7">
@@ -579,7 +579,7 @@
         <v>266</v>
       </c>
       <c r="C7" t="n">
-        <v>5.149398496240601</v>
+        <v>5.134624060150376</v>
       </c>
       <c r="D7" t="n">
         <v>6.065</v>
@@ -588,7 +588,7 @@
         <v>196.3</v>
       </c>
       <c r="F7" t="n">
-        <v>-51.88</v>
+        <v>-52.7</v>
       </c>
     </row>
     <row r="8">

--- a/result/突破幅度分析.xlsx
+++ b/result/突破幅度分析.xlsx
@@ -510,19 +510,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="C4" t="n">
-        <v>3.802307692307692</v>
+        <v>4.103181818181818</v>
       </c>
       <c r="D4" t="n">
-        <v>6.69</v>
+        <v>6.715</v>
       </c>
       <c r="E4" t="n">
         <v>24.07</v>
       </c>
       <c r="F4" t="n">
-        <v>-48.03</v>
+        <v>-50.38</v>
       </c>
     </row>
     <row r="5">
@@ -532,10 +532,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C5" t="n">
-        <v>5.055</v>
+        <v>4.708076923076923</v>
       </c>
       <c r="D5" t="n">
         <v>7.175</v>
@@ -544,7 +544,7 @@
         <v>17.65</v>
       </c>
       <c r="F5" t="n">
-        <v>-39.41</v>
+        <v>-45.49</v>
       </c>
     </row>
     <row r="6">
@@ -554,10 +554,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="C6" t="n">
-        <v>4.703245033112583</v>
+        <v>4.488774193548387</v>
       </c>
       <c r="D6" t="n">
         <v>6.7</v>
@@ -566,7 +566,7 @@
         <v>16.88</v>
       </c>
       <c r="F6" t="n">
-        <v>-61.2</v>
+        <v>-62.26</v>
       </c>
     </row>
     <row r="7">
@@ -576,19 +576,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>266</v>
+        <v>274</v>
       </c>
       <c r="C7" t="n">
-        <v>5.134624060150376</v>
+        <v>5.071459854014599</v>
       </c>
       <c r="D7" t="n">
-        <v>6.065</v>
+        <v>6.08</v>
       </c>
       <c r="E7" t="n">
         <v>196.3</v>
       </c>
       <c r="F7" t="n">
-        <v>-52.7</v>
+        <v>-55.63</v>
       </c>
     </row>
     <row r="8">
@@ -598,13 +598,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C8" t="n">
-        <v>3.589393939393939</v>
+        <v>3.740746268656717</v>
       </c>
       <c r="D8" t="n">
-        <v>-6.75</v>
+        <v>-6.44</v>
       </c>
       <c r="E8" t="n">
         <v>65.02</v>

--- a/result/突破幅度分析.xlsx
+++ b/result/突破幅度分析.xlsx
@@ -510,19 +510,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="C4" t="n">
-        <v>4.103181818181818</v>
+        <v>3.844</v>
       </c>
       <c r="D4" t="n">
-        <v>6.715</v>
+        <v>6.685</v>
       </c>
       <c r="E4" t="n">
         <v>24.07</v>
       </c>
       <c r="F4" t="n">
-        <v>-50.38</v>
+        <v>-47.25</v>
       </c>
     </row>
     <row r="5">
@@ -532,19 +532,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="C5" t="n">
-        <v>4.708076923076923</v>
+        <v>4.459152542372881</v>
       </c>
       <c r="D5" t="n">
-        <v>7.175</v>
+        <v>7.14</v>
       </c>
       <c r="E5" t="n">
         <v>17.65</v>
       </c>
       <c r="F5" t="n">
-        <v>-45.49</v>
+        <v>-50.52</v>
       </c>
     </row>
     <row r="6">
@@ -554,13 +554,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>155</v>
+        <v>168</v>
       </c>
       <c r="C6" t="n">
-        <v>4.488774193548387</v>
+        <v>4.100714285714285</v>
       </c>
       <c r="D6" t="n">
-        <v>6.7</v>
+        <v>6.645</v>
       </c>
       <c r="E6" t="n">
         <v>16.88</v>
@@ -576,19 +576,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>274</v>
+        <v>280</v>
       </c>
       <c r="C7" t="n">
-        <v>5.071459854014599</v>
+        <v>4.7565</v>
       </c>
       <c r="D7" t="n">
-        <v>6.08</v>
+        <v>6.06</v>
       </c>
       <c r="E7" t="n">
         <v>196.3</v>
       </c>
       <c r="F7" t="n">
-        <v>-55.63</v>
+        <v>-55.16</v>
       </c>
     </row>
     <row r="8">
@@ -598,19 +598,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="C8" t="n">
-        <v>3.740746268656717</v>
+        <v>2.754788732394366</v>
       </c>
       <c r="D8" t="n">
-        <v>-6.44</v>
+        <v>-7.06</v>
       </c>
       <c r="E8" t="n">
         <v>65.02</v>
       </c>
       <c r="F8" t="n">
-        <v>-19.77</v>
+        <v>-28.63</v>
       </c>
     </row>
     <row r="9">
